--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8015</v>
+        <v>4.1927</v>
       </c>
       <c r="E2" t="n">
-        <v>3.113</v>
+        <v>2.2958</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6885</v>
+        <v>1.8969</v>
       </c>
       <c r="G2" t="n">
         <v>1.4645</v>
@@ -610,13 +610,13 @@
         <v>1.3648</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7911</v>
+        <v>1.1823</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5446</v>
+        <v>0.7275</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2464</v>
+        <v>0.4548</v>
       </c>
       <c r="V2" t="n">
         <v>1.3185</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6419</v>
+        <v>4.0247</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0609</v>
+        <v>3.7768</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.419</v>
+        <v>0.2479</v>
       </c>
       <c r="G3" t="n">
         <v>0.0815</v>
@@ -688,13 +688,13 @@
         <v>1.1374</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2429</v>
+        <v>0.6256</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1074</v>
+        <v>0.8233</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8645</v>
+        <v>-0.1977</v>
       </c>
       <c r="V3" t="n">
         <v>2.1802</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7219</v>
+        <v>1.8504</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1321</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8541</v>
+        <v>1.1654</v>
       </c>
       <c r="G4" t="n">
         <v>2.2</v>
@@ -766,13 +766,13 @@
         <v>1.5923</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6163</v>
+        <v>-0.4879</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4365</v>
+        <v>-0.6194</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1798</v>
+        <v>0.1315</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3167</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3611</v>
+        <v>-0.9609</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3203</v>
+        <v>-2.6714</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0408</v>
+        <v>1.7105</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.8217</v>
+        <v>0.1382</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1048</v>
+        <v>-1.7444</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.7169</v>
+        <v>1.8825</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.1554</v>
+        <v>-1.2558</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.1967</v>
+        <v>-2.2657</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0413</v>
+        <v>1.0099</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6663</v>
+        <v>1.394</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0919</v>
+        <v>0.5213</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.7582</v>
+        <v>0.8727</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6824</v>
+        <v>0.2275</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8198</v>
+        <v>1.3648</v>
       </c>
       <c r="S6" t="n">
-        <v>0.213</v>
+        <v>-0.2364</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4073</v>
+        <v>-0.2782</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1942</v>
+        <v>0.0418</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5652</v>
+        <v>-1.0901</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5652</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0901</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3671</v>
+        <v>-2.185</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.2551</v>
+        <v>-1.3203</v>
       </c>
       <c r="F7" t="n">
-        <v>0.888</v>
+        <v>-0.8647</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1382</v>
+        <v>-4.8217</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7444</v>
+        <v>-2.1048</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8825</v>
+        <v>-2.7169</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2558</v>
+        <v>-2.1554</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2657</v>
+        <v>-2.1967</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0099</v>
+        <v>0.0413</v>
       </c>
       <c r="M7" t="n">
-        <v>1.394</v>
+        <v>-2.6663</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5213</v>
+        <v>0.0919</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8727</v>
+        <v>-2.7582</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2275</v>
+        <v>0.6824</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3648</v>
+        <v>1.8198</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6426</v>
+        <v>0.3891</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8619</v>
+        <v>0.4073</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.0182</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0901</v>
+        <v>1.5652</v>
       </c>
       <c r="W7" t="n">
+        <v>1.5652</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.0901</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4777</v>
+        <v>-2.6057</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3467</v>
+        <v>-1.4628</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.131</v>
+        <v>-1.1429</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5543</v>
+        <v>-3.2614</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9169</v>
+        <v>-1.1886</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6374</v>
+        <v>-2.0729</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.413</v>
+        <v>-1.2294</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4875</v>
+        <v>-0.6747</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0745</v>
+        <v>-0.5547</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1413</v>
+        <v>-2.032</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4294</v>
+        <v>-0.5138</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7119</v>
+        <v>-1.5182</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9099</v>
+        <v>1.1374</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2275</v>
+        <v>1.1374</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2131</v>
+        <v>-0.3233</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2036</v>
+        <v>-0.2333</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0095</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7734</v>
+        <v>-0.1583</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7734</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2618</v>
+        <v>-2.9182</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1632</v>
+        <v>-2.8136</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0987</v>
+        <v>-0.1046</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2614</v>
+        <v>-2.5543</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1886</v>
+        <v>-1.9169</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0729</v>
+        <v>-0.6374</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2294</v>
+        <v>-1.413</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6747</v>
+        <v>-1.4875</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5547</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.032</v>
+        <v>-1.1413</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5138</v>
+        <v>-0.4294</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5182</v>
+        <v>-0.7119</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1374</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1374</v>
+        <v>0.2275</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9794</v>
+        <v>-0.2275</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9337</v>
+        <v>-0.2633</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0457</v>
+        <v>0.0358</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1583</v>
+        <v>0.7734</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1583</v>
+        <v>0.7734</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.827</v>
+        <v>-3.5255</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8376</v>
+        <v>-1.6551</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9894</v>
+        <v>-1.8704</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8379</v>
+        <v>1.862</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1905</v>
+        <v>0.3638</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0284</v>
+        <v>1.4982</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3003</v>
+        <v>4.8397</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1245</v>
+        <v>0.4276</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1758</v>
+        <v>4.4121</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5376</v>
+        <v>-2.9776</v>
       </c>
       <c r="N10" t="n">
-        <v>0.315</v>
+        <v>-0.0638</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8526</v>
+        <v>-2.9138</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5022</v>
+        <v>-5.2319</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4121</v>
+        <v>-6.8242</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9099</v>
+        <v>1.5923</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3328</v>
+        <v>-0.1556</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6946</v>
+        <v>0.3294</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3617</v>
+        <v>-0.485</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1802</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8281</v>
+        <v>-3.7169</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3555</v>
+        <v>-2.0711</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4725</v>
+        <v>-1.6458</v>
       </c>
       <c r="G11" t="n">
-        <v>1.862</v>
+        <v>-3.8379</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3638</v>
+        <v>0.1905</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4982</v>
+        <v>-4.0284</v>
       </c>
       <c r="J11" t="n">
-        <v>4.8397</v>
+        <v>-1.3003</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4276</v>
+        <v>-0.1245</v>
       </c>
       <c r="L11" t="n">
-        <v>4.4121</v>
+        <v>-1.1758</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9776</v>
+        <v>-2.5376</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0638</v>
+        <v>0.315</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.9138</v>
+        <v>-2.8526</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.2319</v>
+        <v>-2.5022</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.8242</v>
+        <v>-3.4121</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5923</v>
+        <v>0.9099</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4582</v>
+        <v>0.443</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.371</v>
+        <v>0.4611</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0872</v>
+        <v>-0.0181</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.1802</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.018899999999999</v>
+        <v>-5.905799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0079</v>
+        <v>-5.008000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0109</v>
+        <v>-0.8977999999999997</v>
       </c>
       <c r="G12" t="n">
         <v>-8.260199999999998</v>
@@ -1369,7 +1369,7 @@
         <v>-3.572399999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>6.1746</v>
+        <v>6.174600000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-10.8623</v>
@@ -1390,13 +1390,13 @@
         <v>11.3737</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2747</v>
+        <v>0.8382000000000003</v>
       </c>
       <c r="T12" t="n">
         <v>1.1389</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.4135</v>
+        <v>-0.3006</v>
       </c>
       <c r="V12" t="n">
         <v>6.0657</v>
